--- a/pseudodata/9001.xlsx
+++ b/pseudodata/9001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,28 +528,28 @@
         <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.008385368461826853</v>
+        <v>-0.0006416780022490428</v>
       </c>
       <c r="L2" t="n">
-        <v>4.027075123098643e-05</v>
+        <v>0.0006648629327549561</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0004192684230913427</v>
+        <v>-3.208390011245214e-05</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -579,28 +579,28 @@
         <v>0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.008731969435628012</v>
+        <v>-0.0009929663379807283</v>
       </c>
       <c r="L3" t="n">
-        <v>5.458199764245759e-05</v>
+        <v>0.0006554210465559668</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0004365984717814006</v>
+        <v>-4.964831689903642e-05</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -630,28 +630,28 @@
         <v>0.2</v>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.006890671562152369</v>
+        <v>-0.001502897805403627</v>
       </c>
       <c r="L4" t="n">
-        <v>7.834348825989987e-05</v>
+        <v>0.0007061840896615814</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0003445335781076185</v>
+        <v>-7.514489027018133e-05</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -681,28 +681,28 @@
         <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.003276304917075423</v>
+        <v>-0.002250161858546431</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001140648000126668</v>
+        <v>0.0008198163076691653</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0001638152458537712</v>
+        <v>-0.0001125080929273216</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -732,28 +732,28 @@
         <v>0.2</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001769773067969072</v>
+        <v>-0.003336551654094611</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001655823801839347</v>
+        <v>0.001010251639706475</v>
       </c>
       <c r="M6" t="n">
-        <v>8.84886533984536e-05</v>
+        <v>-0.0001668275827047305</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -783,28 +783,28 @@
         <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007760947305080275</v>
+        <v>-0.004883052459919033</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002320242682036076</v>
+        <v>0.00130087172332521</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0003880473652540138</v>
+        <v>-0.0002441526229959517</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -834,28 +834,28 @@
         <v>0.2</v>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01360618803147804</v>
+        <v>-0.007019147149000009</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003076522104915549</v>
+        <v>0.001723684812510854</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0006803094015739021</v>
+        <v>-0.0003509573574500005</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -876,37 +876,37 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="F9" t="n">
         <v>0.1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.009873115651338875</v>
       </c>
       <c r="L9" t="n">
-        <v>4.210895655111789e-05</v>
+        <v>0.002319476445822627</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.0004936557825669438</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -927,37 +927,37 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
         <v>0.1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.01357217216340156</v>
       </c>
       <c r="L10" t="n">
-        <v>5.660608385236017e-05</v>
+        <v>0.003137969489920652</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-0.0006786086081700781</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -978,37 +978,37 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="F11" t="n">
         <v>0.1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.0182361978557409</v>
       </c>
       <c r="L11" t="n">
-        <v>7.899506564468355e-05</v>
+        <v>0.004230353843222565</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-0.0009118098927870452</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1029,37 +1029,37 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
         <v>0.1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.02390611480885951</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0001113373971050318</v>
+        <v>0.00562144900791617</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-0.001195305740442975</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1080,37 +1080,37 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F13" t="n">
         <v>0.1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-0.0303723925995333</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0001570845696119841</v>
+        <v>0.00727173306576096</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0.001518619629976665</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1131,37 +1131,37 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
         <v>0.1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.03712563862779073</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0002167000225829003</v>
+        <v>0.00909851560853483</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-0.001856281931389537</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1182,37 +1182,37 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="F15" t="n">
         <v>0.1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0.04381579921728775</v>
       </c>
       <c r="L15" t="n">
-        <v>0.000284866962799785</v>
+        <v>0.01110041360606876</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0.002190789960864387</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -1233,7 +1233,7 @@
         <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
         <v>0.1</v>
@@ -1242,28 +1242,28 @@
         <v>0.2</v>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0008344592517463651</v>
+        <v>-0.0507724921651375</v>
       </c>
       <c r="L16" t="n">
-        <v>4.027075123098643e-05</v>
+        <v>0.01343880186044152</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.172296258731826e-05</v>
+        <v>-0.002538624608256875</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -1284,7 +1284,7 @@
         <v>100</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.1</v>
@@ -1293,28 +1293,28 @@
         <v>0.2</v>
       </c>
       <c r="H17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.00137301646961569</v>
+        <v>-0.05870820314860616</v>
       </c>
       <c r="L17" t="n">
-        <v>5.458199764245759e-05</v>
+        <v>0.01631615359921252</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.865082348078449e-05</v>
+        <v>-0.002935410157430308</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1335,7 +1335,7 @@
         <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
         <v>0.1</v>
@@ -1344,28 +1344,28 @@
         <v>0.2</v>
       </c>
       <c r="H18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.001460427909525474</v>
+        <v>-0.06777794055456189</v>
       </c>
       <c r="L18" t="n">
-        <v>7.834348825989987e-05</v>
+        <v>0.01971078482533109</v>
       </c>
       <c r="M18" t="n">
-        <v>-7.302139547627372e-05</v>
+        <v>-0.003388897027728095</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1386,37 +1386,37 @@
         <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>0.1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.001097748599520922</v>
+        <v>0.0005029404230396015</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0001140648000126668</v>
+        <v>0.0006175054688146011</v>
       </c>
       <c r="M19" t="n">
-        <v>-5.488742997604608e-05</v>
+        <v>2.514702115198008e-05</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1437,37 +1437,37 @@
         <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="F20" t="n">
         <v>0.1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0004084451751854406</v>
+        <v>0.0006515525686477966</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0001655823801839347</v>
+        <v>0.0006398614317210475</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.042225875927203e-05</v>
+        <v>3.257762843238983e-05</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -1488,37 +1488,37 @@
         <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
         <v>0.1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H21" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0004593860333848787</v>
+        <v>0.0007412908141610911</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0002320242682036076</v>
+        <v>0.00070591523519354</v>
       </c>
       <c r="M21" t="n">
-        <v>2.296930166924394e-05</v>
+        <v>3.706454070805456e-05</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -1539,37 +1539,37 @@
         <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="F22" t="n">
         <v>0.1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H22" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001443872902526759</v>
+        <v>0.0007361754308977042</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0003076522104915549</v>
+        <v>0.0008222431962653888</v>
       </c>
       <c r="M22" t="n">
-        <v>7.219364512633796e-05</v>
+        <v>3.680877154488521e-05</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -1590,7 +1590,7 @@
         <v>100</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
         <v>0.1</v>
@@ -1599,28 +1599,28 @@
         <v>0.5</v>
       </c>
       <c r="H23" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.001020441460806524</v>
+        <v>0.0005951120552177304</v>
       </c>
       <c r="L23" t="n">
-        <v>4.210895655111789e-05</v>
+        <v>0.001002079024783605</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.102207304032619e-05</v>
+        <v>2.975560276088652e-05</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -1641,7 +1641,7 @@
         <v>100</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="F24" t="n">
         <v>0.1</v>
@@ -1650,28 +1650,28 @@
         <v>0.5</v>
       </c>
       <c r="H24" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.001516206341650703</v>
+        <v>0.0002718566742570185</v>
       </c>
       <c r="L24" t="n">
-        <v>5.660608385236017e-05</v>
+        <v>0.001264602501944516</v>
       </c>
       <c r="M24" t="n">
-        <v>-7.581031708253515e-05</v>
+        <v>1.359283371285093e-05</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -1692,7 +1692,7 @@
         <v>100</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
         <v>0.1</v>
@@ -1701,28 +1701,28 @@
         <v>0.5</v>
       </c>
       <c r="H25" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.001576148172237476</v>
+        <v>-0.0002821909102044196</v>
       </c>
       <c r="L25" t="n">
-        <v>7.899506564468355e-05</v>
+        <v>0.001634542301293724</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.880740861187382e-05</v>
+        <v>-1.410954551022098e-05</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -1743,7 +1743,7 @@
         <v>100</v>
       </c>
       <c r="E26" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F26" t="n">
         <v>0.1</v>
@@ -1752,28 +1752,28 @@
         <v>0.5</v>
       </c>
       <c r="H26" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.001221703361196662</v>
+        <v>-0.001114400214244687</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0001113373971050318</v>
+        <v>0.002142527642744749</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.108516805983311e-05</v>
+        <v>-5.572001071223436e-05</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -1794,7 +1794,7 @@
         <v>100</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
         <v>0.1</v>
@@ -1803,28 +1803,28 @@
         <v>0.5</v>
       </c>
       <c r="H27" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.000583323282405782</v>
+        <v>-0.002273179885359515</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0001570845696119841</v>
+        <v>0.002826394349830507</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.91661641202891e-05</v>
+        <v>-0.0001136589942679758</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -1845,7 +1845,7 @@
         <v>100</v>
       </c>
       <c r="E28" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F28" t="n">
         <v>0.1</v>
@@ -1854,28 +1854,28 @@
         <v>0.5</v>
       </c>
       <c r="H28" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0002023342642149885</v>
+        <v>-0.003822114826776744</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0002167000225829003</v>
+        <v>0.003729038132715396</v>
       </c>
       <c r="M28" t="n">
-        <v>1.011671321074943e-05</v>
+        <v>-0.0001911057413388372</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -1896,7 +1896,7 @@
         <v>100</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
         <v>0.1</v>
@@ -1905,28 +1905,28 @@
         <v>0.5</v>
       </c>
       <c r="H29" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>0.001097138855984747</v>
+        <v>-0.005849141680845619</v>
       </c>
       <c r="L29" t="n">
-        <v>0.000284866962799785</v>
+        <v>0.004882232219512518</v>
       </c>
       <c r="M29" t="n">
-        <v>5.485694279923733e-05</v>
+        <v>-0.000292457084042281</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -1947,37 +1947,37 @@
         <v>100</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H30" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K30" t="n">
-        <v>0.000316408192947887</v>
+        <v>-0.00841619630193343</v>
       </c>
       <c r="L30" t="n">
-        <v>4.027075123098643e-05</v>
+        <v>0.006275084506875604</v>
       </c>
       <c r="M30" t="n">
-        <v>1.582040964739435e-05</v>
+        <v>-0.0004208098150966715</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -1998,37 +1998,37 @@
         <v>100</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
         <v>0.1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0003150170930460087</v>
+        <v>-0.01144364401344182</v>
       </c>
       <c r="L31" t="n">
-        <v>5.458199764245759e-05</v>
+        <v>0.007849292232165361</v>
       </c>
       <c r="M31" t="n">
-        <v>1.575085465230044e-05</v>
+        <v>-0.000572182200672091</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2049,37 +2049,37 @@
         <v>100</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="F32" t="n">
         <v>0.1</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0002786036692431717</v>
+        <v>-0.01472729418844253</v>
       </c>
       <c r="L32" t="n">
-        <v>7.834348825989987e-05</v>
+        <v>0.009577554437617725</v>
       </c>
       <c r="M32" t="n">
-        <v>1.393018346215858e-05</v>
+        <v>-0.0007363647094221267</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -2100,37 +2100,37 @@
         <v>100</v>
       </c>
       <c r="E33" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="F33" t="n">
         <v>0.1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H33" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0002044831790415496</v>
+        <v>-0.01820853679078187</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0001140648000126668</v>
+        <v>0.01155409117285207</v>
       </c>
       <c r="M33" t="n">
-        <v>1.022415895207748e-05</v>
+        <v>-0.0009104268395390936</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -2151,37 +2151,37 @@
         <v>100</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="F34" t="n">
         <v>0.1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>7.82471663903943e-05</v>
+        <v>-0.0221644936248199</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0001655823801839347</v>
+        <v>0.0139529566209016</v>
       </c>
       <c r="M34" t="n">
-        <v>3.912358319519715e-06</v>
+        <v>-0.001108224681240995</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -2202,448 +2202,40 @@
         <v>100</v>
       </c>
       <c r="E35" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="F35" t="n">
         <v>0.1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H35" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.0001595791772484259</v>
+        <v>-0.02702054017428415</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0002320242682036076</v>
+        <v>0.01684764016762894</v>
       </c>
       <c r="M35" t="n">
-        <v>-7.978958862421297e-06</v>
+        <v>-0.001351027008714208</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>p</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>100</v>
-      </c>
-      <c r="E36" t="n">
-        <v>5</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H36" t="n">
-        <v>50</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>100</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-0.0003467899696979439</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.0003076522104915549</v>
-      </c>
-      <c r="M36" t="n">
-        <v>-1.733949848489719e-05</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="n">
-        <v>100</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>50</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>100</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.0001402153700578001</v>
-      </c>
-      <c r="L37" t="n">
-        <v>4.210895655111789e-05</v>
-      </c>
-      <c r="M37" t="n">
-        <v>7.010768502890003e-06</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B38" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>100</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H38" t="n">
-        <v>50</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>100</v>
-      </c>
-      <c r="K38" t="n">
-        <v>-0.0001336877093173102</v>
-      </c>
-      <c r="L38" t="n">
-        <v>5.660608385236017e-05</v>
-      </c>
-      <c r="M38" t="n">
-        <v>-6.684385465865513e-06</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B39" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>100</v>
-      </c>
-      <c r="E39" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>50</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>100</v>
-      </c>
-      <c r="K39" t="n">
-        <v>-0.0004269424290267768</v>
-      </c>
-      <c r="L39" t="n">
-        <v>7.899506564468355e-05</v>
-      </c>
-      <c r="M39" t="n">
-        <v>-2.134712145133884e-05</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B40" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>100</v>
-      </c>
-      <c r="E40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>50</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>100</v>
-      </c>
-      <c r="K40" t="n">
-        <v>-0.0007149859297201657</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.0001113373971050318</v>
-      </c>
-      <c r="M40" t="n">
-        <v>-3.574929648600828e-05</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B41" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>100</v>
-      </c>
-      <c r="E41" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H41" t="n">
-        <v>50</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>100</v>
-      </c>
-      <c r="K41" t="n">
-        <v>-0.000971010273575663</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.0001570845696119841</v>
-      </c>
-      <c r="M41" t="n">
-        <v>-4.855051367878315e-05</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="O41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B42" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>100</v>
-      </c>
-      <c r="E42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H42" t="n">
-        <v>50</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>100</v>
-      </c>
-      <c r="K42" t="n">
-        <v>-0.001142184723262885</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.0002167000225829003</v>
-      </c>
-      <c r="M42" t="n">
-        <v>-5.710923616314426e-05</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B43" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>100</v>
-      </c>
-      <c r="E43" t="n">
-        <v>5</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>50</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>100</v>
-      </c>
-      <c r="K43" t="n">
-        <v>-0.001223229843669028</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.000284866962799785</v>
-      </c>
-      <c r="M43" t="n">
-        <v>-6.11614921834514e-05</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="O43" t="n">
         <v>1</v>
       </c>
     </row>
